--- a/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/merged_table.xlsx
+++ b/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/merged_table.xlsx
@@ -413,121 +413,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:X1"/>
+  <dimension ref="B1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Unnamed: 0_x</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>product_id</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Unnamed: 0_y</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Unnamed: 0.1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Unnamed: 0.10</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Unnamed: 0.11</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Unnamed: 0.12</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Unnamed: 0.13</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Unnamed: 0.14</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Unnamed: 0.15</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Unnamed: 0.16</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Unnamed: 0.17</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Unnamed: 0.18</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Unnamed: 0.2</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Unnamed: 0.3</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Unnamed: 0.4</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Unnamed: 0.5</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Unnamed: 0.6</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Unnamed: 0.7</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Unnamed: 0.8</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Unnamed: 0.9</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>product_name</t>
         </is>
